--- a/tests/traces/compare_test_e2e/reference/compare_h100_mi300_qwen.xlsx
+++ b/tests/traces/compare_test_e2e/reference/compare_h100_mi300_qwen.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args_intersect_mi300" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args_only_baseline_m" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args_only_variant_mi" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary_intersect_" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary_only_basel" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary_only_varia" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM_intersect_mi300" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM_only_baseline_mi300" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM_only_variant_mi300" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDPA_fwd_intersect_mi300" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDPA_fwd_only_baseline_mi300" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDPA_fwd_only_variant_mi300" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="un_eltwise_intersect_mi300" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="un_eltwise_only_baseline_mi300" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="un_eltwise_only_variant_mi300" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bin_eltwise_intersect_mi300" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bin_eltwise_only_baseline_mi300" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bin_eltwise_only_variant_mi300" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="kernel_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args_intersect_mi300" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ops_unique_args_only_baseline_m" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ops_unique_args_only_variant_mi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="unified_perf_summary_intersect_" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="unified_perf_summary_only_basel" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="unified_perf_summary_only_varia" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="GEMM_intersect_mi300" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GEMM_only_baseline_mi300" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GEMM_only_variant_mi300" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SDPA_fwd_intersect_mi300" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SDPA_fwd_only_baseline_mi300" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SDPA_fwd_only_variant_mi300" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="un_eltwise_intersect_mi300" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="un_eltwise_only_baseline_mi300" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="un_eltwise_only_variant_mi300" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="bin_eltwise_intersect_mi300" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="bin_eltwise_only_baseline_mi300" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="bin_eltwise_only_variant_mi300" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7834,7 +7834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7865,45 +7865,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>h100::total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_direct_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_subtree_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>h100::Count</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>h100::Categories</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>h100::total_direct_kernel_time_ms</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>h100::Percentage (%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>h100::Cumulative Percentage (%)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_direct_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mi300::Count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mi300::Categories</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mi300::total_direct_kernel_time_ms</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mi300::Percentage (%)</t>
         </is>
@@ -7928,34 +7948,46 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>220</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>6752.89990234375</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.75289990234375</v>
       </c>
       <c r="H2" t="n">
         <v>6.75289990234375</v>
       </c>
       <c r="I2" t="n">
+        <v>220</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>21.16532719371875</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>21.16532719371875</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
+        <v>4541.28857421875</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.54128857421875</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.54128857421875</v>
+      </c>
+      <c r="P2" t="n">
         <v>220</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>4.54128857421875</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>15.26795188172271</v>
       </c>
     </row>
@@ -7978,34 +8010,46 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>6668.681640625</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.668681640625</v>
       </c>
       <c r="H3" t="n">
         <v>6.668681640625</v>
       </c>
       <c r="I3" t="n">
+        <v>96</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>20.90136547493998</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>42.06669266865873</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
+        <v>8663.615234375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8.663615234374999</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8.663615234374999</v>
+      </c>
+      <c r="P3" t="n">
         <v>96</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>{'GEMM'}</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>8.663615234374999</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>29.12734092062252</v>
       </c>
     </row>
@@ -8028,34 +8072,46 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>197</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>5101.934814453125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.101934814453125</v>
       </c>
       <c r="H4" t="n">
         <v>5.101934814453125</v>
       </c>
       <c r="I4" t="n">
+        <v>197</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>15.99077747790201</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>58.05747014656075</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
+        <v>3190.6943359375</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.1906943359375</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.1906943359375</v>
+      </c>
+      <c r="P4" t="n">
         <v>197</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>3.1906943359375</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>10.72721250680696</v>
       </c>
     </row>
@@ -8078,34 +8134,46 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2722.704345703125</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.722704345703125</v>
       </c>
       <c r="H5" t="n">
         <v>2.722704345703125</v>
       </c>
       <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>8.53365652711153</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>66.59112667367228</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
+        <v>4016.34326171875</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.90879833984375</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.01634326171875</v>
+      </c>
+      <c r="P5" t="n">
         <v>24</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>{'other'}</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>3.90879833984375</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>13.14150025763531</v>
       </c>
     </row>
@@ -8128,34 +8196,46 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>145</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>2607.51513671875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.60751513671875</v>
       </c>
       <c r="H6" t="n">
         <v>2.60751513671875</v>
       </c>
       <c r="I6" t="n">
+        <v>145</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>8.17262388445474</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>74.76375055812701</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
+        <v>1895.603515625</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.895603515625</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.895603515625</v>
+      </c>
+      <c r="P6" t="n">
         <v>145</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>1.895603515625</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>6.373077330450393</v>
       </c>
     </row>
@@ -8178,34 +8258,46 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>2329.075927734375</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.329075927734375</v>
       </c>
       <c r="H7" t="n">
         <v>2.329075927734375</v>
       </c>
       <c r="I7" t="n">
+        <v>72</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>7.29992370424488</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>82.06367426237189</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
+        <v>2954.7626953125</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.9547626953125</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.9547626953125</v>
+      </c>
+      <c r="P7" t="n">
         <v>72</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>{'GEMM'}</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>2.9547626953125</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>9.934003073500232</v>
       </c>
     </row>
@@ -8228,34 +8320,46 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2017.782958984375</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.017782958984375</v>
       </c>
       <c r="H8" t="n">
         <v>2.017782958984375</v>
       </c>
       <c r="I8" t="n">
+        <v>49</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>6.324251380949954</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>88.38792564332185</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
+        <v>1356.06982421875</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.35606982421875</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35606982421875</v>
+      </c>
+      <c r="P8" t="n">
         <v>49</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>{'other'}</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>1.35606982421875</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>4.559148463272868</v>
       </c>
     </row>
@@ -8278,34 +8382,46 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>1300.794921875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.300794921875</v>
       </c>
       <c r="H9" t="n">
         <v>1.300794921875</v>
       </c>
       <c r="I9" t="n">
+        <v>49</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>4.077026245251563</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>92.46495188857341</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
+        <v>928.080078125</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.928080078125</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.928080078125</v>
+      </c>
+      <c r="P9" t="n">
         <v>49</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0.928080078125</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>3.120233771454534</v>
       </c>
     </row>
@@ -8328,34 +8444,46 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>925.11474609375</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.92511474609375</v>
       </c>
       <c r="H10" t="n">
         <v>0.92511474609375</v>
       </c>
       <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>2.899547835147452</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>95.36449972372085</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>777.642578125</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.777642578125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.777642578125</v>
+      </c>
+      <c r="P10" t="n">
         <v>24</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>0.777642578125</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>2.61445826882601</v>
       </c>
     </row>
@@ -8378,34 +8506,46 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>743.327392578125</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.743327392578125</v>
       </c>
       <c r="H11" t="n">
         <v>0.743327392578125</v>
       </c>
       <c r="I11" t="n">
+        <v>49</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>2.329779458230888</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>97.69427918195174</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>619.05224609375</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.61905224609375</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.61905224609375</v>
+      </c>
+      <c r="P11" t="n">
         <v>49</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>{'reduce'}</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>0.61905224609375</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>2.081272694118042</v>
       </c>
     </row>
@@ -8428,34 +8568,46 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>587.3271484375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5873271484375</v>
       </c>
       <c r="H12" t="n">
         <v>0.5873271484375</v>
       </c>
       <c r="I12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>1.840834522383346</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>99.53511370433509</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
+        <v>517.09814453125</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.51709814453125</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.51709814453125</v>
+      </c>
+      <c r="P12" t="n">
         <v>48</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>0.51709814453125</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>1.738499868440847</v>
       </c>
     </row>
@@ -8478,34 +8630,46 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>79.076416015625</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.079076416015625</v>
       </c>
       <c r="H13" t="n">
         <v>0.079076416015625</v>
       </c>
       <c r="I13" t="n">
+        <v>49</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>0.2478458502985414</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>99.78295955463363</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>215.44775390625</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.21544775390625</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.21544775390625</v>
+      </c>
+      <c r="P13" t="n">
         <v>49</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>0.21544775390625</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>0.7243419760506528</v>
       </c>
     </row>
@@ -8528,34 +8692,46 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>51.77587890625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05177587890625</v>
       </c>
       <c r="H14" t="n">
         <v>0.05177587890625</v>
       </c>
       <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>0.1622789369960601</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>99.94523849162969</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0210078125</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0210078125</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>{'other'}</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>0.0210078125</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>0.07062891184919506</v>
       </c>
     </row>
@@ -8578,34 +8754,46 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>4.1279296875</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0041279296875</v>
       </c>
       <c r="H15" t="n">
         <v>0.0041279296875</v>
       </c>
       <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>0.01293799459966514</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>99.95817648622936</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0023251953125</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0023251953125</v>
+      </c>
+      <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>{'reduce'}</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>0.0023251953125</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="R15" t="n">
         <v>0.007817378166276191</v>
       </c>
     </row>
@@ -8628,34 +8816,46 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>3.52001953125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.00352001953125</v>
       </c>
       <c r="H16" t="n">
         <v>0.00352001953125</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>0.01103264763058741</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>99.96920913385995</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.027341796875</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.027341796875</v>
+      </c>
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>{'GEMM'}</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0.027341796875</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="R16" t="n">
         <v>0.09192396215850518</v>
       </c>
     </row>
@@ -8678,34 +8878,46 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2.367919921875</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002367919921875</v>
       </c>
       <c r="H17" t="n">
         <v>0.002367919921875</v>
       </c>
       <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>0.007421670784371432</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>99.97663080464432</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.000759765625</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.000759765625</v>
+      </c>
+      <c r="P17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>{'other'}</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>0.000759765625</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="R17" t="n">
         <v>0.002554355402504358</v>
       </c>
     </row>
@@ -8728,34 +8940,46 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>2.080078125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.002080078125</v>
       </c>
       <c r="H18" t="n">
         <v>0.002080078125</v>
       </c>
       <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>0.006519500472506917</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>99.98315030511682</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.00468994140625</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.00468994140625</v>
+      </c>
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>0.00468994140625</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
         <v>0.01576772727574188</v>
       </c>
     </row>
@@ -8778,34 +9002,46 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>2.01611328125</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.00201611328125</v>
       </c>
       <c r="H19" t="n">
         <v>0.00201611328125</v>
       </c>
       <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>0.006319018180981469</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>99.9894693232978</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0042490234375</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0042490234375</v>
+      </c>
+      <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0.0042490234375</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>0.0142853475016664</v>
       </c>
     </row>
@@ -8828,34 +9064,46 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>1.85595703125</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.00185595703125</v>
       </c>
       <c r="H20" t="n">
         <v>0.00185595703125</v>
       </c>
       <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>0.005817047252581877</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>99.99528637055037</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.00557177734375</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.00557177734375</v>
+      </c>
+      <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>0.00557177734375</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>0.01873248682389282</v>
       </c>
     </row>
@@ -8878,34 +9126,46 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>1.50390625</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.00150390625</v>
       </c>
       <c r="H21" t="n">
         <v>0.00150390625</v>
       </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>0.004713629449605941</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>99.99999999999999</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0022841796875</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0022841796875</v>
+      </c>
+      <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>{'other'}</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>0.0022841796875</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
         <v>0.007679482373338938</v>
       </c>
     </row>
@@ -8924,18 +9184,26 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>107.544921875</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.107544921875</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.107544921875</v>
+      </c>
+      <c r="P22" t="n">
         <v>24</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>0.107544921875</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="R22" t="n">
         <v>0.3615693355478085</v>
       </c>
     </row>
@@ -13324,19 +13592,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ36"/>
+  <dimension ref="A1:BC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
     <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
     <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
-    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
-    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
-    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
-    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13427,130 +13703,190 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>h100::total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>h100::total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>h100::total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>h100::total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>h100::total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>h100::total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>h100::total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>h100::ex_UID</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>h100::kernel_details_summary</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>h100::trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>h100::Percentage (%)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>h100::Cumulative Percentage (%)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mi300::op category</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mi300::process_name</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mi300::process_label</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mi300::thread_name</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mi300::operation_count</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_mean</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mi300::ex_UID</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mi300::kernel_details_summary</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mi300::trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mi300::Percentage (%)</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mi300::Cumulative Percentage (%)</t>
         </is>
@@ -13627,97 +13963,133 @@
         <v>84.4844258626302</v>
       </c>
       <c r="R2" t="n">
+        <v>84.4844258626302</v>
+      </c>
+      <c r="S2" t="n">
         <v>84.4635009765625</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
+        <v>84.4635009765625</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.199723729751199</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
+        <v>1.199723729751199</v>
+      </c>
+      <c r="W2" t="n">
         <v>82.27197265625</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
+        <v>82.27197265625</v>
+      </c>
+      <c r="Y2" t="n">
         <v>86.912109375</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
+        <v>86.912109375</v>
+      </c>
+      <c r="AA2" t="n">
         <v>4055.25244140625</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AB2" t="n">
+        <v>4055.25244140625</v>
+      </c>
+      <c r="AC2" t="n">
         <v>215</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(83.66)}]</t>
         </is>
       </c>
-      <c r="Z2" t="n">
+      <c r="AF2" t="n">
         <v>12.71020539571459</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AG2" t="n">
         <v>12.71020539571459</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>GEMM</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AL2" t="n">
         <v>48</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AM2" t="n">
         <v>110.5890299479167</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AN2" t="n">
+        <v>110.5890299479167</v>
+      </c>
+      <c r="AO2" t="n">
         <v>110.452880859375</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AP2" t="n">
+        <v>110.452880859375</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>3.280588398059727</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AR2" t="n">
+        <v>3.280588398059727</v>
+      </c>
+      <c r="AS2" t="n">
         <v>105</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
+        <v>105</v>
+      </c>
+      <c r="AU2" t="n">
         <v>118.55078125</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AV2" t="n">
+        <v>118.55078125</v>
+      </c>
+      <c r="AW2" t="n">
         <v>5308.2734375</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AX2" t="n">
+        <v>5308.2734375</v>
+      </c>
+      <c r="AY2" t="n">
         <v>231</v>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(5308.273), 'mean_duration_us': np.float64(110.58902083333334), 'median_duration_us': np.float64(110.453), 'std_dev_duration_us': np.float64(3.2462516941953186), 'min_duration_us': np.float64(105.0), 'max_duration_us': np.float64(118.551)}]</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x224x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(110.59)}]</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="BB2" t="n">
         <v>17.8465785854006</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BC2" t="n">
         <v>17.8465785854006</v>
       </c>
     </row>
@@ -13792,97 +14164,133 @@
         <v>113.4460144042969</v>
       </c>
       <c r="R3" t="n">
+        <v>113.4460144042969</v>
+      </c>
+      <c r="S3" t="n">
         <v>113.7750244140625</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
+        <v>113.7750244140625</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.173453067400901</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
+        <v>2.173453067400901</v>
+      </c>
+      <c r="W3" t="n">
         <v>109.280029296875</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
+        <v>109.280029296875</v>
+      </c>
+      <c r="Y3" t="n">
         <v>119.64697265625</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
+        <v>119.64697265625</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2722.704345703125</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AB3" t="n">
+        <v>2722.704345703125</v>
+      </c>
+      <c r="AC3" t="n">
         <v>164</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(2722.705), 'mean_duration_us': np.float64(113.44604166666666), 'median_duration_us': np.float64(113.775), 'std_dev_duration_us': np.float64(2.127694555913488), 'min_duration_us': np.float64(109.28), 'max_duration_us': np.float64(119.647)}]</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(113.45)}]</t>
         </is>
       </c>
-      <c r="Z3" t="n">
+      <c r="AF3" t="n">
         <v>8.53365652711153</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AG3" t="n">
         <v>21.24386192282612</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF3" t="n">
+      <c r="AL3" t="n">
         <v>24</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AM3" t="n">
         <v>162.8665974934896</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AN3" t="n">
+        <v>167.3476359049479</v>
+      </c>
+      <c r="AO3" t="n">
         <v>164.237060546875</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AP3" t="n">
+        <v>168.906494140625</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>9.452351716739908</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AR3" t="n">
+        <v>10.23520398355555</v>
+      </c>
+      <c r="AS3" t="n">
         <v>138.55712890625</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
+        <v>139.55908203125</v>
+      </c>
+      <c r="AU3" t="n">
         <v>173.0771484375</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AV3" t="n">
+        <v>177.92724609375</v>
+      </c>
+      <c r="AW3" t="n">
         <v>3908.79833984375</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AX3" t="n">
+        <v>4016.34326171875</v>
+      </c>
+      <c r="AY3" t="n">
         <v>165</v>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>[{'name': 'attn_fwd', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(3908.798), 'mean_duration_us': np.float64(162.86658333333332), 'median_duration_us': np.float64(164.23700000000002), 'std_dev_duration_us': np.float64(9.253315184825505), 'min_duration_us': np.float64(138.557), 'max_duration_us': np.float64(173.077)}]</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>[{'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(162.87)}]</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="BB3" t="n">
         <v>13.14150025763531</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="BC3" t="n">
         <v>30.98807884303591</v>
       </c>
     </row>
@@ -13957,97 +14365,133 @@
         <v>32.34827677408854</v>
       </c>
       <c r="R4" t="n">
+        <v>32.34827677408854</v>
+      </c>
+      <c r="S4" t="n">
         <v>32.3680419921875</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>32.3680419921875</v>
+      </c>
+      <c r="U4" t="n">
         <v>0.3264361462154342</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
+        <v>0.3264361462154342</v>
+      </c>
+      <c r="W4" t="n">
         <v>31.712158203125</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
+        <v>31.712158203125</v>
+      </c>
+      <c r="Y4" t="n">
         <v>33.152099609375</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Z4" t="n">
+        <v>33.152099609375</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2329.075927734375</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AB4" t="n">
+        <v>2329.075927734375</v>
+      </c>
+      <c r="AC4" t="n">
         <v>89</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.87)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.48)}]</t>
         </is>
       </c>
-      <c r="Z4" t="n">
+      <c r="AF4" t="n">
         <v>7.299923704244882</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AG4" t="n">
         <v>28.543785627071</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>GEMM</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF4" t="n">
+      <c r="AL4" t="n">
         <v>72</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AM4" t="n">
         <v>41.03837076822916</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AN4" t="n">
+        <v>41.03837076822916</v>
+      </c>
+      <c r="AO4" t="n">
         <v>40.71240234375</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AP4" t="n">
+        <v>40.71240234375</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.121361742339089</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AR4" t="n">
+        <v>1.121361742339089</v>
+      </c>
+      <c r="AS4" t="n">
         <v>39.56982421875</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
+        <v>39.56982421875</v>
+      </c>
+      <c r="AU4" t="n">
         <v>45.02294921875</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AV4" t="n">
+        <v>45.02294921875</v>
+      </c>
+      <c r="AW4" t="n">
         <v>2954.7626953125</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AX4" t="n">
+        <v>2954.7626953125</v>
+      </c>
+      <c r="AY4" t="n">
         <v>90</v>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 72, 'total_duration_us': np.float64(2954.763), 'mean_duration_us': np.float64(41.038375), 'median_duration_us': np.float64(40.7125), 'std_dev_duration_us': np.float64(1.1135532272552386), 'min_duration_us': np.float64(39.57), 'max_duration_us': np.float64(45.023)}]</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(41.04)}]</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="BB4" t="n">
         <v>9.93400307350023</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="BC4" t="n">
         <v>40.92208191653614</v>
       </c>
     </row>
@@ -14122,97 +14566,133 @@
         <v>29.28038533528646</v>
       </c>
       <c r="R5" t="n">
+        <v>29.28038533528646</v>
+      </c>
+      <c r="S5" t="n">
         <v>29.31201171875</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
+        <v>29.31201171875</v>
+      </c>
+      <c r="U5" t="n">
         <v>0.3233270218510627</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
+        <v>0.3233270218510627</v>
+      </c>
+      <c r="W5" t="n">
         <v>28.672119140625</v>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
+        <v>28.672119140625</v>
+      </c>
+      <c r="Y5" t="n">
         <v>30.048095703125</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Z5" t="n">
+        <v>30.048095703125</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2108.187744140625</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AB5" t="n">
+        <v>2108.187744140625</v>
+      </c>
+      <c r="AC5" t="n">
         <v>145</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2108.187), 'mean_duration_us': np.float64(29.280375), 'median_duration_us': np.float64(29.312), 'std_dev_duration_us': np.float64(0.3210814381594732), 'min_duration_us': np.float64(28.672), 'max_duration_us': np.float64(30.048)}]</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(29.28)}]</t>
         </is>
       </c>
-      <c r="Z5" t="n">
+      <c r="AF5" t="n">
         <v>6.607603257237321</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AG5" t="n">
         <v>35.15138888430833</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF5" t="n">
+      <c r="AL5" t="n">
         <v>72</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AM5" t="n">
         <v>15.11367458767361</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AN5" t="n">
+        <v>15.11367458767361</v>
+      </c>
+      <c r="AO5" t="n">
         <v>15.19287109375</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AP5" t="n">
+        <v>15.19287109375</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>0.5665176534834554</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AR5" t="n">
+        <v>0.5665176534834554</v>
+      </c>
+      <c r="AS5" t="n">
         <v>12.98779296875</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
+        <v>12.98779296875</v>
+      </c>
+      <c r="AU5" t="n">
         <v>16.27587890625</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AV5" t="n">
+        <v>16.27587890625</v>
+      </c>
+      <c r="AW5" t="n">
         <v>1088.1845703125</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AX5" t="n">
+        <v>1088.1845703125</v>
+      </c>
+      <c r="AY5" t="n">
         <v>146</v>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 72, 'total_duration_us': np.float64(1088.184), 'mean_duration_us': np.float64(15.113666666666667), 'median_duration_us': np.float64(15.193), 'std_dev_duration_us': np.float64(0.5625623422242988), 'min_duration_us': np.float64(12.988), 'max_duration_us': np.float64(16.276)}]</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(15.11)}]</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="BB5" t="n">
         <v>3.658509999185101</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="BC5" t="n">
         <v>60.98291891379351</v>
       </c>
     </row>
@@ -14287,97 +14767,133 @@
         <v>41.96514383951823</v>
       </c>
       <c r="R6" t="n">
+        <v>41.96514383951823</v>
+      </c>
+      <c r="S6" t="n">
         <v>41.9678955078125</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
+        <v>41.9678955078125</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.2933502450882166</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
+        <v>0.2933502450882166</v>
+      </c>
+      <c r="W6" t="n">
         <v>41.3759765625</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
+        <v>41.3759765625</v>
+      </c>
+      <c r="Y6" t="n">
         <v>42.464111328125</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
+        <v>42.464111328125</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2014.326904296875</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AB6" t="n">
+        <v>2014.326904296875</v>
+      </c>
+      <c r="AC6" t="n">
         <v>129</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(2014.326), 'mean_duration_us': np.float64(41.965125), 'median_duration_us': np.float64(41.968), 'std_dev_duration_us': np.float64(0.290296301575362), 'min_duration_us': np.float64(41.376), 'max_duration_us': np.float64(42.464)}]</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(41.97)}]</t>
         </is>
       </c>
-      <c r="Z6" t="n">
+      <c r="AF6" t="n">
         <v>6.313419215610892</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AG6" t="n">
         <v>41.46480809991922</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF6" t="n">
+      <c r="AL6" t="n">
         <v>48</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AM6" t="n">
         <v>28.11951700846354</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AN6" t="n">
+        <v>28.11951700846354</v>
+      </c>
+      <c r="AO6" t="n">
         <v>27.90283203125</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AP6" t="n">
+        <v>27.90283203125</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>0.8371311008823814</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AR6" t="n">
+        <v>0.8371311008823814</v>
+      </c>
+      <c r="AS6" t="n">
         <v>26.81982421875</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
+        <v>26.81982421875</v>
+      </c>
+      <c r="AU6" t="n">
         <v>30.34814453125</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AV6" t="n">
+        <v>30.34814453125</v>
+      </c>
+      <c r="AW6" t="n">
         <v>1349.73681640625</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AX6" t="n">
+        <v>1349.73681640625</v>
+      </c>
+      <c r="AY6" t="n">
         <v>130</v>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(1349.738), 'mean_duration_us': np.float64(28.119541666666667), 'median_duration_us': np.float64(27.903), 'std_dev_duration_us': np.float64(0.8283528575415325), 'min_duration_us': np.float64(26.82), 'max_duration_us': np.float64(30.348)}]</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': np.float64(28.12)}]</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="BB6" t="n">
         <v>4.537856696196722</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="BC6" t="n">
         <v>53.444068908235</v>
       </c>
     </row>
@@ -14452,97 +14968,133 @@
         <v>76.47029622395833</v>
       </c>
       <c r="R7" t="n">
+        <v>76.47029622395833</v>
+      </c>
+      <c r="S7" t="n">
         <v>76.4954833984375</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>76.4954833984375</v>
+      </c>
+      <c r="U7" t="n">
         <v>0.4304329398221454</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
+        <v>0.4304329398221454</v>
+      </c>
+      <c r="W7" t="n">
         <v>75.807861328125</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
+        <v>75.807861328125</v>
+      </c>
+      <c r="Y7" t="n">
         <v>77.375</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Z7" t="n">
+        <v>77.375</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1835.287109375</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AB7" t="n">
+        <v>1835.287109375</v>
+      </c>
+      <c r="AC7" t="n">
         <v>235</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.85)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(75.62)}]</t>
         </is>
       </c>
-      <c r="Z7" t="n">
+      <c r="AF7" t="n">
         <v>5.752262394834891</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AG7" t="n">
         <v>47.21707049475411</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>GEMM</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF7" t="n">
+      <c r="AL7" t="n">
         <v>24</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AM7" t="n">
         <v>98.94974772135417</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AN7" t="n">
+        <v>98.94974772135417</v>
+      </c>
+      <c r="AO7" t="n">
         <v>98.324951171875</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AP7" t="n">
+        <v>98.324951171875</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>3.384941704730123</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AR7" t="n">
+        <v>3.384941704730123</v>
+      </c>
+      <c r="AS7" t="n">
         <v>93.65380859375</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
+        <v>93.65380859375</v>
+      </c>
+      <c r="AU7" t="n">
         <v>105.8828125</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AV7" t="n">
+        <v>105.8828125</v>
+      </c>
+      <c r="AW7" t="n">
         <v>2374.7939453125</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AX7" t="n">
+        <v>2374.7939453125</v>
+      </c>
+      <c r="AY7" t="n">
         <v>253</v>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(2374.795), 'mean_duration_us': np.float64(98.94979166666667), 'median_duration_us': np.float64(98.32499999999999), 'std_dev_duration_us': np.float64(3.3136632546066833), 'min_duration_us': np.float64(93.654), 'max_duration_us': np.float64(105.883)}]</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(98.95)}]</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="BB7" t="n">
         <v>7.984130295502148</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="BC7" t="n">
         <v>48.90621221203828</v>
       </c>
     </row>
@@ -14617,97 +15169,133 @@
         <v>34.81449890136719</v>
       </c>
       <c r="R8" t="n">
+        <v>34.81449890136719</v>
+      </c>
+      <c r="S8" t="n">
         <v>34.783935546875</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>34.783935546875</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.3250576438614337</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
+        <v>0.3250576438614337</v>
+      </c>
+      <c r="W8" t="n">
         <v>34.27099609375</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
+        <v>34.27099609375</v>
+      </c>
+      <c r="Y8" t="n">
         <v>35.614990234375</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
+        <v>35.614990234375</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1671.095947265625</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AB8" t="n">
+        <v>1671.095947265625</v>
+      </c>
+      <c r="AC8" t="n">
         <v>131</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1671.096), 'mean_duration_us': np.float64(34.8145), 'median_duration_us': np.float64(34.784), 'std_dev_duration_us': np.float64(0.3216488121124247), 'min_duration_us': np.float64(34.271), 'max_duration_us': np.float64(35.615)}]</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(34.81)}]</t>
         </is>
       </c>
-      <c r="Z8" t="n">
+      <c r="AF8" t="n">
         <v>5.237645012877888</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AG8" t="n">
         <v>52.454715507632</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF8" t="n">
+      <c r="AL8" t="n">
         <v>48</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AM8" t="n">
         <v>20.47682698567708</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AN8" t="n">
+        <v>20.47682698567708</v>
+      </c>
+      <c r="AO8" t="n">
         <v>20.406005859375</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AP8" t="n">
+        <v>20.406005859375</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>0.9517316900632534</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AR8" t="n">
+        <v>0.9517316900632534</v>
+      </c>
+      <c r="AS8" t="n">
         <v>18.8017578125</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
+        <v>18.8017578125</v>
+      </c>
+      <c r="AU8" t="n">
         <v>23.1318359375</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AV8" t="n">
+        <v>23.1318359375</v>
+      </c>
+      <c r="AW8" t="n">
         <v>982.8876953125</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AX8" t="n">
+        <v>982.8876953125</v>
+      </c>
+      <c r="AY8" t="n">
         <v>132</v>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(982.889), 'mean_duration_us': np.float64(20.476854166666666), 'median_duration_us': np.float64(20.406), 'std_dev_duration_us': np.float64(0.94175673587502), 'min_duration_us': np.float64(18.802), 'max_duration_us': np.float64(23.132)}]</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(20.48)}]</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="BB8" t="n">
         <v>3.304498666383521</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="BC8" t="n">
         <v>67.8359064359972</v>
       </c>
     </row>
@@ -14782,97 +15370,133 @@
         <v>32.83514528858419</v>
       </c>
       <c r="R9" t="n">
+        <v>32.83514528858419</v>
+      </c>
+      <c r="S9" t="n">
         <v>32.639892578125</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>32.639892578125</v>
+      </c>
+      <c r="U9" t="n">
         <v>0.4306580406298848</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
+        <v>0.4306580406298848</v>
+      </c>
+      <c r="W9" t="n">
         <v>32.256103515625</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
+        <v>32.256103515625</v>
+      </c>
+      <c r="Y9" t="n">
         <v>33.886962890625</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
+        <v>33.886962890625</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1608.922119140625</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AB9" t="n">
+        <v>1608.922119140625</v>
+      </c>
+      <c r="AC9" t="n">
         <v>77</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1608.9229999999998), 'mean_duration_us': np.float64(32.835163265306115), 'median_duration_us': np.float64(32.64), 'std_dev_duration_us': np.float64(0.42625121207266925), 'min_duration_us': np.float64(32.256), 'max_duration_us': np.float64(33.887)}]</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 2, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.84)}]</t>
         </is>
       </c>
-      <c r="Z9" t="n">
+      <c r="AF9" t="n">
         <v>5.042776225515153</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AG9" t="n">
         <v>57.49749173314716</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF9" t="n">
+      <c r="AL9" t="n">
         <v>49</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AM9" t="n">
         <v>23.55439851721939</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AN9" t="n">
+        <v>23.55439851721939</v>
+      </c>
+      <c r="AO9" t="n">
         <v>23.453125</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AP9" t="n">
+        <v>23.453125</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.710600521974922</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AR9" t="n">
+        <v>1.710600521974922</v>
+      </c>
+      <c r="AS9" t="n">
         <v>18.44091796875</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
+        <v>18.44091796875</v>
+      </c>
+      <c r="AU9" t="n">
         <v>27.22119140625</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AV9" t="n">
+        <v>27.22119140625</v>
+      </c>
+      <c r="AW9" t="n">
         <v>1154.16552734375</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AX9" t="n">
+        <v>1154.16552734375</v>
+      </c>
+      <c r="AY9" t="n">
         <v>78</v>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(1154.1640000000002), 'mean_duration_us': np.float64(23.55436734693878), 'median_duration_us': np.float64(23.453), 'std_dev_duration_us': np.float64(1.6930433736488344), 'min_duration_us': np.float64(18.441), 'max_duration_us': np.float64(27.221)}]</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(23.55)}]</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="BB9" t="n">
         <v>3.880340006373412</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="BC9" t="n">
         <v>57.32440891460841</v>
       </c>
     </row>
@@ -14947,97 +15571,133 @@
         <v>32.03850809733073</v>
       </c>
       <c r="R10" t="n">
+        <v>32.03850809733073</v>
+      </c>
+      <c r="S10" t="n">
         <v>32</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>32</v>
+      </c>
+      <c r="U10" t="n">
         <v>0.3186166119751925</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
+        <v>0.3186166119751925</v>
+      </c>
+      <c r="W10" t="n">
         <v>31.552001953125</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
+        <v>31.552001953125</v>
+      </c>
+      <c r="Y10" t="n">
         <v>32.672119140625</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Z10" t="n">
+        <v>32.672119140625</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1537.848388671875</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AB10" t="n">
+        <v>1537.848388671875</v>
+      </c>
+      <c r="AC10" t="n">
         <v>123</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1537.849), 'mean_duration_us': np.float64(32.03852083333333), 'median_duration_us': np.float64(32.0), 'std_dev_duration_us': np.float64(0.31526120054007917), 'min_duration_us': np.float64(31.552), 'max_duration_us': np.float64(32.672)}]</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(32.04)}]</t>
         </is>
       </c>
-      <c r="Z10" t="n">
+      <c r="AF10" t="n">
         <v>4.820012852445286</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AG10" t="n">
         <v>62.31750458559245</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF10" t="n">
+      <c r="AL10" t="n">
         <v>48</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AM10" t="n">
         <v>19.89802042643229</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AN10" t="n">
+        <v>19.89802042643229</v>
+      </c>
+      <c r="AO10" t="n">
         <v>20.044921875</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AP10" t="n">
+        <v>20.044921875</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>1.092918112053265</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AR10" t="n">
+        <v>1.092918112053265</v>
+      </c>
+      <c r="AS10" t="n">
         <v>18.12109375</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
+        <v>18.12109375</v>
+      </c>
+      <c r="AU10" t="n">
         <v>22.73095703125</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AV10" t="n">
+        <v>22.73095703125</v>
+      </c>
+      <c r="AW10" t="n">
         <v>955.10498046875</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AX10" t="n">
+        <v>955.10498046875</v>
+      </c>
+      <c r="AY10" t="n">
         <v>124</v>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(955.105), 'mean_duration_us': np.float64(19.898020833333334), 'median_duration_us': np.float64(20.045), 'std_dev_duration_us': np.float64(1.0814598060334801), 'min_duration_us': np.float64(18.121), 'max_duration_us': np.float64(22.731)}]</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(19.9)}]</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="BB10" t="n">
         <v>3.21109232445094</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="BC10" t="n">
         <v>74.34363080016792</v>
       </c>
     </row>
@@ -15112,97 +15772,133 @@
         <v>29.21780333227041</v>
       </c>
       <c r="R11" t="n">
+        <v>29.21780333227041</v>
+      </c>
+      <c r="S11" t="n">
         <v>29.216064453125</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
+        <v>29.216064453125</v>
+      </c>
+      <c r="U11" t="n">
         <v>0.6723608131569377</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
+        <v>0.6723608131569377</v>
+      </c>
+      <c r="W11" t="n">
         <v>25.2470703125</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
+        <v>25.2470703125</v>
+      </c>
+      <c r="Y11" t="n">
         <v>30.049072265625</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Z11" t="n">
+        <v>30.049072265625</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1431.67236328125</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AB11" t="n">
+        <v>1431.67236328125</v>
+      </c>
+      <c r="AC11" t="n">
         <v>70</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1431.6720000000003), 'mean_duration_us': np.float64(29.21779591836735), 'median_duration_us': np.float64(29.216), 'std_dev_duration_us': np.float64(0.6654753090251477), 'min_duration_us': np.float64(25.247), 'max_duration_us': np.float64(30.049)}]</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(29.22)}]</t>
         </is>
       </c>
-      <c r="Z11" t="n">
+      <c r="AF11" t="n">
         <v>4.48722984810352</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AG11" t="n">
         <v>66.80473443369597</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF11" t="n">
+      <c r="AL11" t="n">
         <v>49</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AM11" t="n">
         <v>21.53999920280612</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AN11" t="n">
+        <v>21.53999920280612</v>
+      </c>
+      <c r="AO11" t="n">
         <v>21.68896484375</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AP11" t="n">
+        <v>21.68896484375</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>0.9070504525026997</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AR11" t="n">
+        <v>0.9070504525026997</v>
+      </c>
+      <c r="AS11" t="n">
         <v>17.72021484375</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
+        <v>17.72021484375</v>
+      </c>
+      <c r="AU11" t="n">
         <v>23.01220703125</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AV11" t="n">
+        <v>23.01220703125</v>
+      </c>
+      <c r="AW11" t="n">
         <v>1055.4599609375</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AX11" t="n">
+        <v>1055.4599609375</v>
+      </c>
+      <c r="AY11" t="n">
         <v>71</v>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(1055.46), 'mean_duration_us': np.float64(21.54), 'median_duration_us': np.float64(21.689), 'std_dev_duration_us': np.float64(0.8977721405381941), 'min_duration_us': np.float64(17.72), 'max_duration_us': np.float64(23.012)}]</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(21.54)}]</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="BB11" t="n">
         <v>3.548488855820164</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="BC11" t="n">
         <v>64.53140776961368</v>
       </c>
     </row>
@@ -15277,97 +15973,133 @@
         <v>26.54683514030612</v>
       </c>
       <c r="R12" t="n">
+        <v>26.54683514030612</v>
+      </c>
+      <c r="S12" t="n">
         <v>26.39990234375</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
+        <v>26.39990234375</v>
+      </c>
+      <c r="U12" t="n">
         <v>0.4194831695891557</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
+        <v>0.4194831695891557</v>
+      </c>
+      <c r="W12" t="n">
         <v>26.048095703125</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
+        <v>26.048095703125</v>
+      </c>
+      <c r="Y12" t="n">
         <v>27.552001953125</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Z12" t="n">
+        <v>27.552001953125</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1300.794921875</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AB12" t="n">
+        <v>1300.794921875</v>
+      </c>
+      <c r="AC12" t="n">
         <v>71</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1300.7949999999998), 'mean_duration_us': np.float64(26.546836734693873), 'median_duration_us': np.float64(26.4), 'std_dev_duration_us': np.float64(0.41517418753759416), 'min_duration_us': np.float64(26.048), 'max_duration_us': np.float64(27.552)}]</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(26.55)}]</t>
         </is>
       </c>
-      <c r="Z12" t="n">
+      <c r="AF12" t="n">
         <v>4.077026245251564</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AG12" t="n">
         <v>70.88176067894753</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF12" t="n">
+      <c r="AL12" t="n">
         <v>49</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AM12" t="n">
         <v>18.94040975765306</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AN12" t="n">
+        <v>18.94040975765306</v>
+      </c>
+      <c r="AO12" t="n">
         <v>19.001953125</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AP12" t="n">
+        <v>19.001953125</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>1.348781311268545</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AR12" t="n">
+        <v>1.348781311268545</v>
+      </c>
+      <c r="AS12" t="n">
         <v>14.03076171875</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
+        <v>14.03076171875</v>
+      </c>
+      <c r="AU12" t="n">
         <v>21.93017578125</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AV12" t="n">
+        <v>21.93017578125</v>
+      </c>
+      <c r="AW12" t="n">
         <v>928.080078125</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AX12" t="n">
+        <v>928.080078125</v>
+      </c>
+      <c r="AY12" t="n">
         <v>72</v>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(928.082), 'mean_duration_us': np.float64(18.940448979591835), 'median_duration_us': np.float64(19.002), 'std_dev_duration_us': np.float64(1.334943231403638), 'min_duration_us': np.float64(14.031), 'max_duration_us': np.float64(21.93)}]</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(18.94)}]</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="BB12" t="n">
         <v>3.120233771454533</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="BC12" t="n">
         <v>77.46386457162245</v>
       </c>
     </row>
@@ -15442,97 +16174,133 @@
         <v>25.18325494260204</v>
       </c>
       <c r="R13" t="n">
+        <v>25.18325494260204</v>
+      </c>
+      <c r="S13" t="n">
         <v>25.087890625</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
+        <v>25.087890625</v>
+      </c>
+      <c r="U13" t="n">
         <v>0.3972371439579201</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
+        <v>0.3972371439579201</v>
+      </c>
+      <c r="W13" t="n">
         <v>24.575927734375</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
+        <v>24.575927734375</v>
+      </c>
+      <c r="Y13" t="n">
         <v>26.14404296875</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Z13" t="n">
+        <v>26.14404296875</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1233.9794921875</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AB13" t="n">
+        <v>1233.9794921875</v>
+      </c>
+      <c r="AC13" t="n">
         <v>82</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(1233.979), 'mean_duration_us': np.float64(25.183244897959185), 'median_duration_us': np.float64(25.088), 'std_dev_duration_us': np.float64(0.3931505673357448), 'min_duration_us': np.float64(24.576), 'max_duration_us': np.float64(26.144)}]</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(25.18)}]</t>
         </is>
       </c>
-      <c r="Z13" t="n">
+      <c r="AF13" t="n">
         <v>3.867609483360272</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AG13" t="n">
         <v>74.7493701623078</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF13" t="n">
+      <c r="AL13" t="n">
         <v>49</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AM13" t="n">
         <v>16.26974051339286</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AN13" t="n">
+        <v>16.26974051339286</v>
+      </c>
+      <c r="AO13" t="n">
         <v>16.0361328125</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AP13" t="n">
+        <v>16.0361328125</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>1.155779257306736</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AR13" t="n">
+        <v>1.155779257306736</v>
+      </c>
+      <c r="AS13" t="n">
         <v>13.02880859375</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
+        <v>13.02880859375</v>
+      </c>
+      <c r="AU13" t="n">
         <v>18.52197265625</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AV13" t="n">
+        <v>18.52197265625</v>
+      </c>
+      <c r="AW13" t="n">
         <v>797.21728515625</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AX13" t="n">
+        <v>797.21728515625</v>
+      </c>
+      <c r="AY13" t="n">
         <v>83</v>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(797.2189999999999), 'mean_duration_us': np.float64(16.26977551020408), 'median_duration_us': np.float64(16.036), 'std_dev_duration_us': np.float64(1.143927913836056), 'min_duration_us': np.float64(13.029), 'max_duration_us': np.float64(18.522)}]</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(16.27)}]</t>
         </is>
       </c>
-      <c r="AP13" t="n">
+      <c r="BB13" t="n">
         <v>2.680269036005314</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="BC13" t="n">
         <v>83.20055938413375</v>
       </c>
     </row>
@@ -15607,97 +16375,133 @@
         <v>51.13045247395834</v>
       </c>
       <c r="R14" t="n">
+        <v>51.13045247395834</v>
+      </c>
+      <c r="S14" t="n">
         <v>51.0718994140625</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
+        <v>51.0718994140625</v>
+      </c>
+      <c r="U14" t="n">
         <v>0.6307408003200445</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
+        <v>0.6307408003200445</v>
+      </c>
+      <c r="W14" t="n">
         <v>50.176025390625</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
+        <v>50.176025390625</v>
+      </c>
+      <c r="Y14" t="n">
         <v>52.094970703125</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Z14" t="n">
+        <v>52.094970703125</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1227.130859375</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AB14" t="n">
+        <v>1227.130859375</v>
+      </c>
+      <c r="AC14" t="n">
         <v>227</v>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1227.131), 'mean_duration_us': np.float64(51.13045833333334), 'median_duration_us': np.float64(51.072), 'std_dev_duration_us': np.float64(0.617469161117019), 'min_duration_us': np.float64(50.176), 'max_duration_us': np.float64(52.095)}]</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Bi...', 'stream': 7, 'mean_duration_us': np.float64(51.13)}]</t>
         </is>
       </c>
-      <c r="Z14" t="n">
+      <c r="AF14" t="n">
         <v>3.846144104574502</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AG14" t="n">
         <v>78.5955142668823</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF14" t="n">
+      <c r="AL14" t="n">
         <v>24</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AM14" t="n">
         <v>37.87921142578125</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AN14" t="n">
+        <v>37.87921142578125</v>
+      </c>
+      <c r="AO14" t="n">
         <v>37.464599609375</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AP14" t="n">
+        <v>37.464599609375</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>1.628049214737037</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AR14" t="n">
+        <v>1.628049214737037</v>
+      </c>
+      <c r="AS14" t="n">
         <v>35.39990234375</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
+        <v>35.39990234375</v>
+      </c>
+      <c r="AU14" t="n">
         <v>42.4970703125</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AV14" t="n">
+        <v>42.4970703125</v>
+      </c>
+      <c r="AW14" t="n">
         <v>909.10107421875</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AX14" t="n">
+        <v>909.10107421875</v>
+      </c>
+      <c r="AY14" t="n">
         <v>245</v>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(909.1), 'mean_duration_us': np.float64(37.87916666666667), 'median_duration_us': np.float64(37.4645), 'std_dev_duration_us': np.float64(1.5937641154059015), 'min_duration_us': np.float64(35.4), 'max_duration_us': np.float64(42.497)}]</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(37.88)}]</t>
         </is>
       </c>
-      <c r="AP14" t="n">
+      <c r="BB14" t="n">
         <v>3.056425776505985</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="BC14" t="n">
         <v>80.52029034812844</v>
       </c>
     </row>
@@ -15772,97 +16576,133 @@
         <v>23.78922526041667</v>
       </c>
       <c r="R15" t="n">
+        <v>23.78922526041667</v>
+      </c>
+      <c r="S15" t="n">
         <v>23.77587890625</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
+        <v>23.77587890625</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.1826717306685092</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
+        <v>0.1826717306685092</v>
+      </c>
+      <c r="W15" t="n">
         <v>23.39208984375</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
+        <v>23.39208984375</v>
+      </c>
+      <c r="Y15" t="n">
         <v>24.35205078125</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Z15" t="n">
+        <v>24.35205078125</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1141.8828125</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AB15" t="n">
+        <v>1141.8828125</v>
+      </c>
+      <c r="AC15" t="n">
         <v>130</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(1141.883), 'mean_duration_us': np.float64(23.78922916666667), 'median_duration_us': np.float64(23.776), 'std_dev_duration_us': np.float64(0.18074236263063953), 'min_duration_us': np.float64(23.392), 'max_duration_us': np.float64(24.352)}]</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(23.79)}]</t>
         </is>
       </c>
-      <c r="Z15" t="n">
+      <c r="AF15" t="n">
         <v>3.578954773942098</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AG15" t="n">
         <v>82.17446904082441</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF15" t="n">
+      <c r="AL15" t="n">
         <v>48</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AM15" t="n">
         <v>14.96426391601562</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AN15" t="n">
+        <v>14.96426391601562</v>
+      </c>
+      <c r="AO15" t="n">
         <v>14.873046875</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AP15" t="n">
+        <v>14.873046875</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>0.5173983809662352</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AR15" t="n">
+        <v>0.5173983809662352</v>
+      </c>
+      <c r="AS15" t="n">
         <v>13.14892578125</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
+        <v>13.14892578125</v>
+      </c>
+      <c r="AU15" t="n">
         <v>16.55712890625</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AV15" t="n">
+        <v>16.55712890625</v>
+      </c>
+      <c r="AW15" t="n">
         <v>718.28466796875</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AX15" t="n">
+        <v>718.28466796875</v>
+      </c>
+      <c r="AY15" t="n">
         <v>131</v>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(718.2850000000001), 'mean_duration_us': np.float64(14.964270833333336), 'median_duration_us': np.float64(14.873), 'std_dev_duration_us': np.float64(0.511951932134231), 'min_duration_us': np.float64(13.149), 'max_duration_us': np.float64(16.557)}]</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(14.96)}]</t>
         </is>
       </c>
-      <c r="AP15" t="n">
+      <c r="BB15" t="n">
         <v>2.4148951489639</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="BC15" t="n">
         <v>88.22991280192366</v>
       </c>
     </row>
@@ -15937,97 +16777,133 @@
         <v>38.54644775390625</v>
       </c>
       <c r="R16" t="n">
+        <v>38.54644775390625</v>
+      </c>
+      <c r="S16" t="n">
         <v>38.4158935546875</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
+        <v>38.4158935546875</v>
+      </c>
+      <c r="U16" t="n">
         <v>0.3625162870903211</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
+        <v>0.3625162870903211</v>
+      </c>
+      <c r="W16" t="n">
         <v>38.14404296875</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
+        <v>38.14404296875</v>
+      </c>
+      <c r="Y16" t="n">
         <v>39.263916015625</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Z16" t="n">
+        <v>39.263916015625</v>
+      </c>
+      <c r="AA16" t="n">
         <v>925.11474609375</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AB16" t="n">
+        <v>925.11474609375</v>
+      </c>
+      <c r="AC16" t="n">
         <v>217</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(925.115), 'mean_duration_us': np.float64(38.546458333333334), 'median_duration_us': np.float64(38.416), 'std_dev_duration_us': np.float64(0.35488331171042203), 'min_duration_us': np.float64(38.144), 'max_duration_us': np.float64(39.264)}]</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 7, 'mean_duration_us': np.float64(38.55)}]</t>
         </is>
       </c>
-      <c r="Z16" t="n">
+      <c r="AF16" t="n">
         <v>2.899547835147452</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AG16" t="n">
         <v>85.07401687597186</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF16" t="n">
+      <c r="AL16" t="n">
         <v>24</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AM16" t="n">
         <v>32.40177408854166</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AN16" t="n">
+        <v>32.40177408854166</v>
+      </c>
+      <c r="AO16" t="n">
         <v>32.27294921875</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AP16" t="n">
+        <v>32.27294921875</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>0.8776191306910622</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AR16" t="n">
+        <v>0.8776191306910622</v>
+      </c>
+      <c r="AS16" t="n">
         <v>31.47119140625</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
+        <v>31.47119140625</v>
+      </c>
+      <c r="AU16" t="n">
         <v>35.080078125</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AV16" t="n">
+        <v>35.080078125</v>
+      </c>
+      <c r="AW16" t="n">
         <v>777.642578125</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AX16" t="n">
+        <v>777.642578125</v>
+      </c>
+      <c r="AY16" t="n">
         <v>234</v>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(777.643), 'mean_duration_us': np.float64(32.40179166666667), 'median_duration_us': np.float64(32.272999999999996), 'std_dev_duration_us': np.float64(0.8591138835629157), 'min_duration_us': np.float64(31.471), 'max_duration_us': np.float64(35.08)}]</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(32.4)}]</t>
         </is>
       </c>
-      <c r="AP16" t="n">
+      <c r="BB16" t="n">
         <v>2.61445826882601</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="BC16" t="n">
         <v>85.81501765295977</v>
       </c>
     </row>
@@ -16102,97 +16978,133 @@
         <v>18.33525490274235</v>
       </c>
       <c r="R17" t="n">
+        <v>18.33525490274235</v>
+      </c>
+      <c r="S17" t="n">
         <v>18.239990234375</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
+        <v>18.239990234375</v>
+      </c>
+      <c r="U17" t="n">
         <v>0.3646247760047354</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>0.3646247760047354</v>
+      </c>
+      <c r="W17" t="n">
         <v>17.85498046875</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
+        <v>17.85498046875</v>
+      </c>
+      <c r="Y17" t="n">
         <v>19.52001953125</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Z17" t="n">
+        <v>19.52001953125</v>
+      </c>
+      <c r="AA17" t="n">
         <v>898.427490234375</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AB17" t="n">
+        <v>898.427490234375</v>
+      </c>
+      <c r="AC17" t="n">
         <v>81</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(898.427), 'mean_duration_us': np.float64(18.335244897959186), 'median_duration_us': np.float64(18.24), 'std_dev_duration_us': np.float64(0.36088720215331926), 'min_duration_us': np.float64(17.855), 'max_duration_us': np.float64(19.52)}]</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(18.34)}]</t>
         </is>
       </c>
-      <c r="Z17" t="n">
+      <c r="AF17" t="n">
         <v>2.81590310320494</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AG17" t="n">
         <v>87.88991997917681</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF17" t="n">
+      <c r="AL17" t="n">
         <v>49</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AM17" t="n">
         <v>13.90765505420918</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AN17" t="n">
+        <v>13.90765505420918</v>
+      </c>
+      <c r="AO17" t="n">
         <v>13.7900390625</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AP17" t="n">
+        <v>13.7900390625</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>0.8931457341508564</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AR17" t="n">
+        <v>0.8931457341508564</v>
+      </c>
+      <c r="AS17" t="n">
         <v>10.14208984375</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
+        <v>10.14208984375</v>
+      </c>
+      <c r="AU17" t="n">
         <v>15.71484375</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AV17" t="n">
+        <v>15.71484375</v>
+      </c>
+      <c r="AW17" t="n">
         <v>681.47509765625</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AX17" t="n">
+        <v>681.47509765625</v>
+      </c>
+      <c r="AY17" t="n">
         <v>82</v>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(681.476), 'mean_duration_us': np.float64(13.907673469387754), 'median_duration_us': np.float64(13.79), 'std_dev_duration_us': np.float64(0.8839741751642698), 'min_duration_us': np.float64(10.142), 'max_duration_us': np.float64(15.715)}]</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="BA17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(13.91)}]</t>
         </is>
       </c>
-      <c r="AP17" t="n">
+      <c r="BB17" t="n">
         <v>2.291140241269046</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="BC17" t="n">
         <v>92.83887776201169</v>
       </c>
     </row>
@@ -16267,97 +17179,133 @@
         <v>17.80457051595052</v>
       </c>
       <c r="R18" t="n">
+        <v>17.80457051595052</v>
+      </c>
+      <c r="S18" t="n">
         <v>17.85595703125</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
+        <v>17.85595703125</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.5205274181052388</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>0.5205274181052388</v>
+      </c>
+      <c r="W18" t="n">
         <v>17.055908203125</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
+        <v>17.055908203125</v>
+      </c>
+      <c r="Y18" t="n">
         <v>19.008056640625</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Z18" t="n">
+        <v>19.008056640625</v>
+      </c>
+      <c r="AA18" t="n">
         <v>854.619384765625</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AB18" t="n">
+        <v>854.619384765625</v>
+      </c>
+      <c r="AC18" t="n">
         <v>191</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(854.619), 'mean_duration_us': np.float64(17.8045625), 'median_duration_us': np.float64(17.856), 'std_dev_duration_us': np.float64(0.5150970744371872), 'min_duration_us': np.float64(17.056), 'max_duration_us': np.float64(19.008)}]</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(17.8)}]</t>
         </is>
       </c>
-      <c r="Z18" t="n">
+      <c r="AF18" t="n">
         <v>2.678597219896759</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AG18" t="n">
         <v>90.56851719907357</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF18" t="n">
+      <c r="AL18" t="n">
         <v>48</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AM18" t="n">
         <v>14.36275227864583</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AN18" t="n">
+        <v>14.36275227864583</v>
+      </c>
+      <c r="AO18" t="n">
         <v>14.35205078125</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AP18" t="n">
+        <v>14.35205078125</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>0.5517010273075365</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AR18" t="n">
+        <v>0.5517010273075365</v>
+      </c>
+      <c r="AS18" t="n">
         <v>13.6298828125</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
+        <v>13.6298828125</v>
+      </c>
+      <c r="AU18" t="n">
         <v>16.7177734375</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AV18" t="n">
+        <v>16.7177734375</v>
+      </c>
+      <c r="AW18" t="n">
         <v>689.412109375</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AX18" t="n">
+        <v>689.412109375</v>
+      </c>
+      <c r="AY18" t="n">
         <v>207</v>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(689.413), 'mean_duration_us': np.float64(14.362770833333334), 'median_duration_us': np.float64(14.352), 'std_dev_duration_us': np.float64(0.5459252558570988), 'min_duration_us': np.float64(13.63), 'max_duration_us': np.float64(16.718)}]</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(14.36)}]</t>
         </is>
       </c>
-      <c r="AP18" t="n">
+      <c r="BB18" t="n">
         <v>2.317824718818987</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="BC18" t="n">
         <v>90.54773752074264</v>
       </c>
     </row>
@@ -16432,97 +17380,133 @@
         <v>32.42258707682291</v>
       </c>
       <c r="R19" t="n">
+        <v>32.42258707682291</v>
+      </c>
+      <c r="S19" t="n">
         <v>32.4000244140625</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>32.4000244140625</v>
+      </c>
+      <c r="U19" t="n">
         <v>0.1504456175239329</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
+        <v>0.1504456175239329</v>
+      </c>
+      <c r="W19" t="n">
         <v>32.192138671875</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
+        <v>32.192138671875</v>
+      </c>
+      <c r="Y19" t="n">
         <v>32.7041015625</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Z19" t="n">
+        <v>32.7041015625</v>
+      </c>
+      <c r="AA19" t="n">
         <v>778.14208984375</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AB19" t="n">
+        <v>778.14208984375</v>
+      </c>
+      <c r="AC19" t="n">
         <v>189</v>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.59)}]</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AF19" t="n">
         <v>2.438897684390508</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AG19" t="n">
         <v>93.00741488346408</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>GEMM</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF19" t="n">
+      <c r="AL19" t="n">
         <v>24</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AM19" t="n">
         <v>40.85616048177084</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AN19" t="n">
+        <v>40.85616048177084</v>
+      </c>
+      <c r="AO19" t="n">
         <v>40.532470703125</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AP19" t="n">
+        <v>40.532470703125</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>1.381501226013306</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AR19" t="n">
+        <v>1.381501226013306</v>
+      </c>
+      <c r="AS19" t="n">
         <v>39.208984375</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
+        <v>39.208984375</v>
+      </c>
+      <c r="AU19" t="n">
         <v>44.94287109375</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AV19" t="n">
+        <v>44.94287109375</v>
+      </c>
+      <c r="AW19" t="n">
         <v>980.5478515625</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AX19" t="n">
+        <v>980.5478515625</v>
+      </c>
+      <c r="AY19" t="n">
         <v>204</v>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(980.549), 'mean_duration_us': np.float64(40.856208333333335), 'median_duration_us': np.float64(40.5325), 'std_dev_duration_us': np.float64(1.3524004269928913), 'min_duration_us': np.float64(39.209), 'max_duration_us': np.float64(44.943)}]</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(40.86)}]</t>
         </is>
       </c>
-      <c r="AP19" t="n">
+      <c r="BB19" t="n">
         <v>3.296632039719767</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="BC19" t="n">
         <v>71.13253847571697</v>
       </c>
     </row>
@@ -16597,97 +17581,133 @@
         <v>15.16994678730867</v>
       </c>
       <c r="R20" t="n">
+        <v>15.16994678730867</v>
+      </c>
+      <c r="S20" t="n">
         <v>15.072021484375</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
+        <v>15.072021484375</v>
+      </c>
+      <c r="U20" t="n">
         <v>0.4689977659830294</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
+        <v>0.4689977659830294</v>
+      </c>
+      <c r="W20" t="n">
         <v>14.176025390625</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
+        <v>14.176025390625</v>
+      </c>
+      <c r="Y20" t="n">
         <v>16.448974609375</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Z20" t="n">
+        <v>16.448974609375</v>
+      </c>
+      <c r="AA20" t="n">
         <v>743.327392578125</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AB20" t="n">
+        <v>743.327392578125</v>
+      </c>
+      <c r="AC20" t="n">
         <v>74</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(743.3270000000001), 'mean_duration_us': np.float64(15.169938775510206), 'median_duration_us': np.float64(15.072), 'std_dev_duration_us': np.float64(0.46419596531071383), 'min_duration_us': np.float64(14.176), 'max_duration_us': np.float64(16.449)}]</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 7, 'mean_duration_us': np.float64(15.17)}]</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AF20" t="n">
         <v>2.329779458230888</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AG20" t="n">
         <v>95.33719434169497</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>reduce</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AK20" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF20" t="n">
+      <c r="AL20" t="n">
         <v>49</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AM20" t="n">
         <v>12.63371930803571</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AN20" t="n">
+        <v>12.63371930803571</v>
+      </c>
+      <c r="AO20" t="n">
         <v>12.828125</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AP20" t="n">
+        <v>12.828125</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>0.9666591045204423</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AR20" t="n">
+        <v>0.9666591045204423</v>
+      </c>
+      <c r="AS20" t="n">
         <v>8.01708984375</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
+        <v>8.01708984375</v>
+      </c>
+      <c r="AU20" t="n">
         <v>13.87109375</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AV20" t="n">
+        <v>13.87109375</v>
+      </c>
+      <c r="AW20" t="n">
         <v>619.05224609375</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AX20" t="n">
+        <v>619.05224609375</v>
+      </c>
+      <c r="AY20" t="n">
         <v>75</v>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(619.053), 'mean_duration_us': np.float64(12.633734693877551), 'median_duration_us': np.float64(12.828), 'std_dev_duration_us': np.float64(0.9567734633782996), 'min_duration_us': np.float64(8.017), 'max_duration_us': np.float64(13.871)}]</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 0, 'mean_duration_us': np.float64(12.63)}]</t>
         </is>
       </c>
-      <c r="AP20" t="n">
+      <c r="BB20" t="n">
         <v>2.081272694118042</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="BC20" t="n">
         <v>94.92015045612973</v>
       </c>
     </row>
@@ -16762,97 +17782,133 @@
         <v>27.42001342773438</v>
       </c>
       <c r="R21" t="n">
+        <v>27.42001342773438</v>
+      </c>
+      <c r="S21" t="n">
         <v>27.4560546875</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
+        <v>27.4560546875</v>
+      </c>
+      <c r="U21" t="n">
         <v>0.2265912406627222</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
+        <v>0.2265912406627222</v>
+      </c>
+      <c r="W21" t="n">
         <v>26.9130859375</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
+        <v>26.9130859375</v>
+      </c>
+      <c r="Y21" t="n">
         <v>27.8720703125</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Z21" t="n">
+        <v>27.8720703125</v>
+      </c>
+      <c r="AA21" t="n">
         <v>658.080322265625</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AB21" t="n">
+        <v>658.080322265625</v>
+      </c>
+      <c r="AC21" t="n">
         <v>179</v>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(658.0799999999999), 'mean_duration_us': np.float64(27.419999999999998), 'median_duration_us': np.float64(27.456), 'std_dev_duration_us': np.float64(0.2218289506203673), 'min_duration_us': np.float64(26.913), 'max_duration_us': np.float64(27.872)}]</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(27.42)}]</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AF21" t="n">
         <v>2.062593188396829</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AG21" t="n">
         <v>97.3997875300918</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF21" t="n">
+      <c r="AL21" t="n">
         <v>24</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AM21" t="n">
         <v>14.97515869140625</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AN21" t="n">
+        <v>14.97515869140625</v>
+      </c>
+      <c r="AO21" t="n">
         <v>14.99365234375</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AP21" t="n">
+        <v>14.99365234375</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>0.4748121556323812</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AR21" t="n">
+        <v>0.4748121556323812</v>
+      </c>
+      <c r="AS21" t="n">
         <v>14.0322265625</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
+        <v>14.0322265625</v>
+      </c>
+      <c r="AU21" t="n">
         <v>15.794921875</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AV21" t="n">
+        <v>15.794921875</v>
+      </c>
+      <c r="AW21" t="n">
         <v>359.40380859375</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AX21" t="n">
+        <v>359.40380859375</v>
+      </c>
+      <c r="AY21" t="n">
         <v>194</v>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(359.404), 'mean_duration_us': np.float64(14.975166666666667), 'median_duration_us': np.float64(14.993500000000001), 'std_dev_duration_us': np.float64(0.464862315338878), 'min_duration_us': np.float64(14.032), 'max_duration_us': np.float64(15.795)}]</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(14.98)}]</t>
         </is>
       </c>
-      <c r="AP21" t="n">
+      <c r="BB21" t="n">
         <v>1.208326660161925</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="BC21" t="n">
         <v>97.8669769847325</v>
       </c>
     </row>
@@ -16927,97 +17983,133 @@
         <v>12.23598225911458</v>
       </c>
       <c r="R22" t="n">
+        <v>12.23598225911458</v>
+      </c>
+      <c r="S22" t="n">
         <v>12.19189453125</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
+        <v>12.19189453125</v>
+      </c>
+      <c r="U22" t="n">
         <v>0.339127372422647</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
+        <v>0.339127372422647</v>
+      </c>
+      <c r="W22" t="n">
         <v>11.615966796875</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
+        <v>11.615966796875</v>
+      </c>
+      <c r="Y22" t="n">
         <v>13.280029296875</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Z22" t="n">
+        <v>13.280029296875</v>
+      </c>
+      <c r="AA22" t="n">
         <v>587.3271484375</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AB22" t="n">
+        <v>587.3271484375</v>
+      </c>
+      <c r="AC22" t="n">
         <v>128</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(587.328), 'mean_duration_us': np.float64(12.235999999999999), 'median_duration_us': np.float64(12.192), 'std_dev_duration_us': np.float64(0.3355813363900522), 'min_duration_us': np.float64(11.616), 'max_duration_us': np.float64(13.28)}]</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(12.24)}]</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AF22" t="n">
         <v>1.840834522383346</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AG22" t="n">
         <v>99.24062205247515</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF22" t="n">
+      <c r="AL22" t="n">
         <v>48</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AM22" t="n">
         <v>10.77287801106771</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AN22" t="n">
+        <v>10.77287801106771</v>
+      </c>
+      <c r="AO22" t="n">
         <v>10.90380859375</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AP22" t="n">
+        <v>10.90380859375</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>0.7221992437648039</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AR22" t="n">
+        <v>0.7221992437648039</v>
+      </c>
+      <c r="AS22" t="n">
         <v>8.37890625</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AT22" t="n">
+        <v>8.37890625</v>
+      </c>
+      <c r="AU22" t="n">
         <v>11.9072265625</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AV22" t="n">
+        <v>11.9072265625</v>
+      </c>
+      <c r="AW22" t="n">
         <v>517.09814453125</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AX22" t="n">
+        <v>517.09814453125</v>
+      </c>
+      <c r="AY22" t="n">
         <v>129</v>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(517.0999999999999), 'mean_duration_us': np.float64(10.772916666666665), 'median_duration_us': np.float64(10.904), 'std_dev_duration_us': np.float64(0.7146025070313955), 'min_duration_us': np.float64(8.379), 'max_duration_us': np.float64(11.907)}]</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="BA22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(10.77)}]</t>
         </is>
       </c>
-      <c r="AP22" t="n">
+      <c r="BB22" t="n">
         <v>1.738499868440847</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="BC22" t="n">
         <v>96.65865032457057</v>
       </c>
     </row>
@@ -17092,97 +18184,133 @@
         <v>1.669383769132653</v>
       </c>
       <c r="R23" t="n">
+        <v>1.669383769132653</v>
+      </c>
+      <c r="S23" t="n">
         <v>1.632080078125</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
+        <v>1.632080078125</v>
+      </c>
+      <c r="U23" t="n">
         <v>0.0834552892669608</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
+        <v>0.0834552892669608</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.568115234375</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.951904296875</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Z23" t="n">
+        <v>1.951904296875</v>
+      </c>
+      <c r="AA23" t="n">
         <v>81.7998046875</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AB23" t="n">
+        <v>81.7998046875</v>
+      </c>
+      <c r="AC23" t="n">
         <v>75</v>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(81.797), 'mean_duration_us': np.float64(1.669326530612245), 'median_duration_us': np.float64(1.632), 'std_dev_duration_us': np.float64(0.08264514449362109), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.952)}]</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(1.67)}]</t>
         </is>
       </c>
-      <c r="Z23" t="n">
+      <c r="AF23" t="n">
         <v>0.2563816516800925</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AG23" t="n">
         <v>99.49700370415523</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AH23" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF23" t="n">
+      <c r="AL23" t="n">
         <v>49</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AM23" t="n">
         <v>4.557218590561225</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AN23" t="n">
+        <v>4.557218590561225</v>
+      </c>
+      <c r="AO23" t="n">
         <v>4.68896484375</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AP23" t="n">
+        <v>4.68896484375</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>0.6582204563524422</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AR23" t="n">
+        <v>0.6582204563524422</v>
+      </c>
+      <c r="AS23" t="n">
         <v>1.60205078125</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AT23" t="n">
+        <v>1.60205078125</v>
+      </c>
+      <c r="AU23" t="n">
         <v>5.33203125</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AV23" t="n">
+        <v>5.33203125</v>
+      </c>
+      <c r="AW23" t="n">
         <v>223.3037109375</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AX23" t="n">
+        <v>223.3037109375</v>
+      </c>
+      <c r="AY23" t="n">
         <v>76</v>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(223.305), 'mean_duration_us': np.float64(4.557244897959184), 'median_duration_us': np.float64(4.689), 'std_dev_duration_us': np.float64(0.6514750462936834), 'min_duration_us': np.float64(1.602), 'max_duration_us': np.float64(5.332)}]</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="BA23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.56)}]</t>
         </is>
       </c>
-      <c r="AP23" t="n">
+      <c r="BB23" t="n">
         <v>0.7507539452478844</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="BC23" t="n">
         <v>98.61773092998038</v>
       </c>
     </row>
@@ -17257,97 +18385,133 @@
         <v>1.613804408482143</v>
       </c>
       <c r="R24" t="n">
+        <v>1.613804408482143</v>
+      </c>
+      <c r="S24" t="n">
         <v>1.60009765625</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
+        <v>1.60009765625</v>
+      </c>
+      <c r="U24" t="n">
         <v>0.1026021369823694</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
+        <v>0.1026021369823694</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.535888671875</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
+        <v>1.535888671875</v>
+      </c>
+      <c r="Y24" t="n">
         <v>2.176025390625</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Z24" t="n">
+        <v>2.176025390625</v>
+      </c>
+      <c r="AA24" t="n">
         <v>79.076416015625</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AB24" t="n">
+        <v>79.076416015625</v>
+      </c>
+      <c r="AC24" t="n">
         <v>76</v>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 49, 'total_duration_us': np.float64(79.073), 'mean_duration_us': np.float64(1.613734693877551), 'median_duration_us': np.float64(1.6), 'std_dev_duration_us': np.float64(0.10155782016738636), 'min_duration_us': np.float64(1.536), 'max_duration_us': np.float64(2.176)}]</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rs...', 'stream': 7, 'mean_duration_us': np.float64(1.61)}]</t>
         </is>
       </c>
-      <c r="Z24" t="n">
+      <c r="AF24" t="n">
         <v>0.2478458502985415</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AG24" t="n">
         <v>99.74484955445378</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF24" t="n">
+      <c r="AL24" t="n">
         <v>49</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AM24" t="n">
         <v>4.396892936862245</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AN24" t="n">
+        <v>4.396892936862245</v>
+      </c>
+      <c r="AO24" t="n">
         <v>4.4501953125</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AP24" t="n">
+        <v>4.4501953125</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>0.5811734917147134</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AR24" t="n">
+        <v>0.5811734917147134</v>
+      </c>
+      <c r="AS24" t="n">
         <v>1.72314453125</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AT24" t="n">
+        <v>1.72314453125</v>
+      </c>
+      <c r="AU24" t="n">
         <v>4.93017578125</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AV24" t="n">
+        <v>4.93017578125</v>
+      </c>
+      <c r="AW24" t="n">
         <v>215.44775390625</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AX24" t="n">
+        <v>215.44775390625</v>
+      </c>
+      <c r="AY24" t="n">
         <v>77</v>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(215.44599999999997), 'mean_duration_us': np.float64(4.396857142857142), 'median_duration_us': np.float64(4.45), 'std_dev_duration_us': np.float64(0.5752471341137846), 'min_duration_us': np.float64(1.723), 'max_duration_us': np.float64(4.93)}]</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="BA24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rs...', 'stream': 0, 'mean_duration_us': np.float64(4.4)}]</t>
         </is>
       </c>
-      <c r="AP24" t="n">
+      <c r="BB24" t="n">
         <v>0.7243419760506526</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="BC24" t="n">
         <v>99.34207290603104</v>
       </c>
     </row>
@@ -17424,91 +18588,123 @@
       <c r="R25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>51.77587890625</v>
+      </c>
       <c r="T25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>51.77587890625</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>51.77587890625</v>
+      </c>
+      <c r="AC25" t="n">
         <v>4</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(51.776), 'mean_duration_us': np.float64(51.776), 'median_duration_us': np.float64(51.776), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.776), 'max_duration_us': np.float64(51.776)}]</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 7, 'mean_duration_us': np.float64(51.78)}]</t>
         </is>
       </c>
-      <c r="Z25" t="n">
+      <c r="AF25" t="n">
         <v>0.1622789369960601</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AG25" t="n">
         <v>99.90712849144984</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AK25" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF25" t="n">
+      <c r="AL25" t="n">
         <v>1</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AM25" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AN25" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="n">
+      <c r="AO25" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AP25" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AT25" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="AY25" t="n">
         <v>4</v>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(21.008), 'mean_duration_us': np.float64(21.008), 'median_duration_us': np.float64(21.008), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(21.008), 'max_duration_us': np.float64(21.008)}]</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(21.01)}]</t>
         </is>
       </c>
-      <c r="AP25" t="n">
+      <c r="BB25" t="n">
         <v>0.07062891184919505</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="BC25" t="n">
         <v>99.86619511558655</v>
       </c>
     </row>
@@ -17585,91 +18781,123 @@
       <c r="R26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>4.1279296875</v>
+      </c>
       <c r="T26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>4.1279296875</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>4.1279296875</v>
+      </c>
+      <c r="AC26" t="n">
         <v>15</v>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(4.128), 'mean_duration_us': np.float64(4.128), 'median_duration_us': np.float64(4.128), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(4.128)}]</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool...', 'stream': 7, 'mean_duration_us': np.float64(4.13)}]</t>
         </is>
       </c>
-      <c r="Z26" t="n">
+      <c r="AF26" t="n">
         <v>0.01293799459966514</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AG26" t="n">
         <v>99.92006648604951</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>reduce</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AK26" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF26" t="n">
+      <c r="AL26" t="n">
         <v>1</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AM26" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AN26" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="n">
+      <c r="AO26" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AP26" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AT26" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="AY26" t="n">
         <v>15</v>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.325), 'mean_duration_us': np.float64(2.325), 'median_duration_us': np.float64(2.325), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.325), 'max_duration_us': np.float64(2.325)}]</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="BA26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool...', 'stream': 0, 'mean_duration_us': np.float64(2.33)}]</t>
         </is>
       </c>
-      <c r="AP26" t="n">
+      <c r="BB26" t="n">
         <v>0.007817378166276191</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="BC26" t="n">
         <v>99.98976616222416</v>
       </c>
     </row>
@@ -17746,91 +18974,123 @@
       <c r="R27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>3.52001953125</v>
+      </c>
       <c r="T27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>3.52001953125</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="AC27" t="n">
         <v>50</v>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1&gt;(cutlass_80_simt_sgemm_128x32_8x5_nn_align1::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.52), 'mean_duration_us': np.float64(3.52), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.52), 'max_duration_us': np.float64(3.52)}]</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_simt_sgemm_128x32_8x5_nn_align1...', 'stream': 7, 'mean_duration_us': np.float64(3.52)}]</t>
         </is>
       </c>
-      <c r="Z27" t="n">
+      <c r="AF27" t="n">
         <v>0.01103264763058741</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AG27" t="n">
         <v>99.93109913368009</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>GEMM</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AK27" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF27" t="n">
+      <c r="AL27" t="n">
         <v>1</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AM27" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AN27" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="n">
+      <c r="AO27" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AP27" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AT27" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="AY27" t="n">
         <v>50</v>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Ailk_Bljk_S_B_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB8_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(27.342), 'mean_duration_us': np.float64(27.342), 'median_duration_us': np.float64(27.342), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(27.342), 'max_duration_us': np.float64(27.342)}]</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="BA27" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Ailk_Bljk_S_B_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_...', 'stream': 0, 'mean_duration_us': np.float64(27.34)}]</t>
         </is>
       </c>
-      <c r="AP27" t="n">
+      <c r="BB27" t="n">
         <v>0.09192396215850518</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="BC27" t="n">
         <v>99.79556620373735</v>
       </c>
     </row>
@@ -17907,91 +19167,123 @@
       <c r="R28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>3.4560546875</v>
+      </c>
       <c r="T28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>3.4560546875</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.4560546875</v>
+      </c>
+      <c r="AC28" t="n">
         <v>54</v>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.456), 'mean_duration_us': np.float64(3.456), 'median_duration_us': np.float64(3.456), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.456), 'max_duration_us': np.float64(3.456)}]</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 7, 'mean_duration_us': np.float64(3.46)}]</t>
         </is>
       </c>
-      <c r="Z28" t="n">
+      <c r="AF28" t="n">
         <v>0.01083216533906196</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AG28" t="n">
         <v>99.94193129901916</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF28" t="n">
+      <c r="AL28" t="n">
         <v>1</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AM28" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AN28" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="n">
+      <c r="AO28" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AP28" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AT28" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="AY28" t="n">
         <v>55</v>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(6.333), 'mean_duration_us': np.float64(6.333), 'median_duration_us': np.float64(6.333), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.333), 'max_duration_us': np.float64(6.333)}]</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="BA28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': np.float64(6.33)}]</t>
         </is>
       </c>
-      <c r="AP28" t="n">
+      <c r="BB28" t="n">
         <v>0.02129176707614494</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="BC28" t="n">
         <v>99.91241647208585</v>
       </c>
     </row>
@@ -18069,94 +19361,130 @@
         <v>1.568115234375</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.568115234375</v>
       </c>
       <c r="T29" t="n">
         <v>1.568115234375</v>
       </c>
       <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.568115234375</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.568115234375</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3.13623046875</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AB29" t="n">
+        <v>3.13623046875</v>
+      </c>
+      <c r="AC29" t="n">
         <v>57</v>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(3.136), 'mean_duration_us': np.float64(1.568), 'median_duration_us': np.float64(1.568), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.568), 'max_duration_us': np.float64(1.568)}]</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.57)}]</t>
         </is>
       </c>
-      <c r="Z29" t="n">
+      <c r="AF29" t="n">
         <v>0.009829753881434726</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AG29" t="n">
         <v>99.95176105290059</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AK29" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF29" t="n">
+      <c r="AL29" t="n">
         <v>2</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AM29" t="n">
         <v>3.70751953125</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AN29" t="n">
         <v>3.70751953125</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AO29" t="n">
+        <v>3.70751953125</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>3.70751953125</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>0.1422499969965125</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AR29" t="n">
+        <v>0.1422499969965125</v>
+      </c>
+      <c r="AS29" t="n">
         <v>3.60693359375</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AT29" t="n">
+        <v>3.60693359375</v>
+      </c>
+      <c r="AU29" t="n">
         <v>3.80810546875</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AV29" t="n">
+        <v>3.80810546875</v>
+      </c>
+      <c r="AW29" t="n">
         <v>7.4150390625</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AX29" t="n">
+        <v>7.4150390625</v>
+      </c>
+      <c r="AY29" t="n">
         <v>58</v>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 2, 'total_duration_us': np.float64(7.415), 'mean_duration_us': np.float64(3.7075), 'median_duration_us': np.float64(3.7075), 'std_dev_duration_us': np.float64(0.10049999999999981), 'min_duration_us': np.float64(3.607), 'max_duration_us': np.float64(3.808)}]</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="BA29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(3.71)}]</t>
         </is>
       </c>
-      <c r="AP29" t="n">
+      <c r="BB29" t="n">
         <v>0.02492958942315629</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="BC29" t="n">
         <v>99.8911247050097</v>
       </c>
     </row>
@@ -18234,94 +19562,130 @@
         <v>1.4874267578125</v>
       </c>
       <c r="S30" t="n">
+        <v>1.4874267578125</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.4874267578125</v>
+      </c>
+      <c r="U30" t="n">
         <v>0.02330552135258396</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
+        <v>0.02330552135258396</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.470947265625</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
+        <v>1.470947265625</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Z30" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.974853515625</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AB30" t="n">
+        <v>2.974853515625</v>
+      </c>
+      <c r="AC30" t="n">
         <v>62</v>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(2.975), 'mean_duration_us': np.float64(1.4875), 'median_duration_us': np.float64(1.4875), 'std_dev_duration_us': np.float64(0.01649999999999996), 'min_duration_us': np.float64(1.471), 'max_duration_us': np.float64(1.504)}]</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 7, 'mean_duration_us': np.float64(1.49)}]</t>
         </is>
       </c>
-      <c r="Z30" t="n">
+      <c r="AF30" t="n">
         <v>0.009323956955105258</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AG30" t="n">
         <v>99.96108500985569</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AK30" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF30" t="n">
+      <c r="AL30" t="n">
         <v>2</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AM30" t="n">
         <v>1.54248046875</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AN30" t="n">
         <v>1.54248046875</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AO30" t="n">
+        <v>1.54248046875</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.54248046875</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>0.02900242657210449</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AR30" t="n">
+        <v>0.02900242657210449</v>
+      </c>
+      <c r="AS30" t="n">
         <v>1.52197265625</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AT30" t="n">
+        <v>1.52197265625</v>
+      </c>
+      <c r="AU30" t="n">
         <v>1.56298828125</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AV30" t="n">
+        <v>1.56298828125</v>
+      </c>
+      <c r="AW30" t="n">
         <v>3.0849609375</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AX30" t="n">
+        <v>3.0849609375</v>
+      </c>
+      <c r="AY30" t="n">
         <v>63</v>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 2, 'total_duration_us': np.float64(3.085), 'mean_duration_us': np.float64(1.5425), 'median_duration_us': np.float64(1.5425), 'std_dev_duration_us': np.float64(0.020499999999999963), 'min_duration_us': np.float64(1.522), 'max_duration_us': np.float64(1.563)}]</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="BA30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(1.54)}]</t>
         </is>
       </c>
-      <c r="AP30" t="n">
+      <c r="BB30" t="n">
         <v>0.01037173356878055</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="BC30" t="n">
         <v>99.98194878405788</v>
       </c>
     </row>
@@ -18398,91 +19762,123 @@
       <c r="R31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>2.592041015625</v>
+      </c>
       <c r="T31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>2.592041015625</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.592041015625</v>
+      </c>
+      <c r="AC31" t="n">
         <v>38</v>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, 4, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt; &gt;(int, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, TrivialOffsetCalculator&lt;1, unsigned int&gt;, at::native::memory::LoadWithCast&lt;1&gt;, at::native::memory::StoreWithCast&lt;1&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.592), 'mean_duration_us': np.float64(2.592), 'median_duration_us': np.float64(2.592), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.592), 'max_duration_us': np.float64(2.592)}]</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::unrolled_elementwise_kernel&lt;at::native::direct_...', 'stream': 7, 'mean_duration_us': np.float64(2.59)}]</t>
         </is>
       </c>
-      <c r="Z31" t="n">
+      <c r="AF31" t="n">
         <v>0.008124124004296473</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AG31" t="n">
         <v>99.96920913385999</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AK31" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF31" t="n">
+      <c r="AL31" t="n">
         <v>1</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AM31" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AN31" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="n">
+      <c r="AO31" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AP31" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AT31" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="AY31" t="n">
         <v>38</v>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(3.086), 'mean_duration_us': np.float64(3.086), 'median_duration_us': np.float64(3.086), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.086), 'max_duration_us': np.float64(3.086)}]</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="BA31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(3.09)}]</t>
         </is>
       </c>
-      <c r="AP31" t="n">
+      <c r="BB31" t="n">
         <v>0.01037501680194572</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="BC31" t="n">
         <v>99.9715770504891</v>
       </c>
     </row>
@@ -18559,91 +19955,123 @@
       <c r="R32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>2.367919921875</v>
+      </c>
       <c r="T32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>2.367919921875</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.367919921875</v>
+      </c>
+      <c r="AC32" t="n">
         <v>19</v>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoH (Device -&gt; Pinned)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.368), 'mean_duration_us': np.float64(2.368), 'median_duration_us': np.float64(2.368), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.368), 'max_duration_us': np.float64(2.368)}]</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoH (Device -&gt; Pinned)', 'stream': 7, 'mean_duration_us': np.float64(2.37)}]</t>
         </is>
       </c>
-      <c r="Z32" t="n">
+      <c r="AF32" t="n">
         <v>0.007421670784371432</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AG32" t="n">
         <v>99.97663080464436</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AH32" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AK32" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF32" t="n">
+      <c r="AL32" t="n">
         <v>1</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AM32" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AN32" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="n">
+      <c r="AO32" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AP32" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AT32" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="AY32" t="n">
         <v>19</v>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(0.76), 'mean_duration_us': np.float64(0.76), 'median_duration_us': np.float64(0.76), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(0.76), 'max_duration_us': np.float64(0.76)}]</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="BA32" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(0.76)}]</t>
         </is>
       </c>
-      <c r="AP32" t="n">
+      <c r="BB32" t="n">
         <v>0.002554355402504358</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="BC32" t="n">
         <v>100</v>
       </c>
     </row>
@@ -18720,91 +20148,123 @@
       <c r="R33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>2.080078125</v>
+      </c>
       <c r="T33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>2.080078125</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.080078125</v>
+      </c>
+      <c r="AC33" t="n">
         <v>55</v>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.08), 'mean_duration_us': np.float64(2.08), 'median_duration_us': np.float64(2.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.08), 'max_duration_us': np.float64(2.08)}]</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 7, 'mean_duration_us': np.float64(2.08)}]</t>
         </is>
       </c>
-      <c r="Z33" t="n">
+      <c r="AF33" t="n">
         <v>0.006519500472506919</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AG33" t="n">
         <v>99.98315030511687</v>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AH33" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AK33" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF33" t="n">
+      <c r="AL33" t="n">
         <v>1</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AM33" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AN33" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="n">
+      <c r="AO33" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AP33" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AT33" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="AY33" t="n">
         <v>56</v>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.69), 'mean_duration_us': np.float64(4.69), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.69), 'max_duration_us': np.float64(4.69)}]</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="BA33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 0, 'mean_duration_us': np.float64(4.69)}]</t>
         </is>
       </c>
-      <c r="AP33" t="n">
+      <c r="BB33" t="n">
         <v>0.01576772727574188</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="BC33" t="n">
         <v>99.94691668618549</v>
       </c>
     </row>
@@ -18881,91 +20341,123 @@
       <c r="R34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>2.01611328125</v>
+      </c>
       <c r="T34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>2.01611328125</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.01611328125</v>
+      </c>
+      <c r="AC34" t="n">
         <v>56</v>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.016), 'mean_duration_us': np.float64(2.016), 'median_duration_us': np.float64(2.016), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.016), 'max_duration_us': np.float64(2.016)}]</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 7, 'mean_duration_us': np.float64(2.02)}]</t>
         </is>
       </c>
-      <c r="Z34" t="n">
+      <c r="AF34" t="n">
         <v>0.00631901818098147</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AG34" t="n">
         <v>99.98946932329784</v>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AH34" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF34" t="n">
+      <c r="AL34" t="n">
         <v>1</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AM34" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AN34" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="n">
+      <c r="AO34" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AP34" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AT34" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="AY34" t="n">
         <v>57</v>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.249), 'mean_duration_us': np.float64(4.249), 'median_duration_us': np.float64(4.249), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(4.249)}]</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
+      <c r="BA34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(4.25)}]</t>
         </is>
       </c>
-      <c r="AP34" t="n">
+      <c r="BB34" t="n">
         <v>0.0142853475016664</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="BC34" t="n">
         <v>99.96120203368716</v>
       </c>
     </row>
@@ -19042,91 +20534,123 @@
       <c r="R35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>1.85595703125</v>
+      </c>
       <c r="T35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>1.85595703125</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.85595703125</v>
+      </c>
+      <c r="AC35" t="n">
         <v>14</v>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.856), 'mean_duration_us': np.float64(1.856), 'median_duration_us': np.float64(1.856), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.856), 'max_duration_us': np.float64(1.856)}]</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1.86)}]</t>
         </is>
       </c>
-      <c r="Z35" t="n">
+      <c r="AF35" t="n">
         <v>0.005817047252581877</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AG35" t="n">
         <v>99.99528637055042</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AH35" t="inlineStr">
         <is>
           <t>elementwise</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AK35" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF35" t="n">
+      <c r="AL35" t="n">
         <v>1</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AM35" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AN35" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="n">
+      <c r="AO35" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AP35" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AT35" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="AY35" t="n">
         <v>14</v>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(5.572), 'mean_duration_us': np.float64(5.572), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.572), 'max_duration_us': np.float64(5.572)}]</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="BA35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(5.57)}]</t>
         </is>
       </c>
-      <c r="AP35" t="n">
+      <c r="BB35" t="n">
         <v>0.01873248682389282</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="BC35" t="n">
         <v>99.93114895890974</v>
       </c>
     </row>
@@ -19203,91 +20727,123 @@
       <c r="R36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>1.50390625</v>
+      </c>
       <c r="T36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>1.50390625</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.50390625</v>
+      </c>
+      <c r="AC36" t="n">
         <v>10</v>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(1.504), 'mean_duration_us': np.float64(1.504), 'median_duration_us': np.float64(1.504), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(1.504), 'max_duration_us': np.float64(1.504)}]</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 7, 'mean_duration_us': np.float64(1.5)}]</t>
         </is>
       </c>
-      <c r="Z36" t="n">
+      <c r="AF36" t="n">
         <v>0.004713629449605941</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AG36" t="n">
         <v>100</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AH36" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AK36" t="inlineStr">
         <is>
           <t>thread 23232 (python3)</t>
         </is>
       </c>
-      <c r="AF36" t="n">
+      <c r="AL36" t="n">
         <v>1</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AM36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AN36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="n">
+      <c r="AO36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AP36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AT36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="AY36" t="n">
         <v>10</v>
       </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.284), 'mean_duration_us': np.float64(2.284), 'median_duration_us': np.float64(2.284), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.284), 'max_duration_us': np.float64(2.284)}]</t>
         </is>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="BA36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': np.float64(2.28)}]</t>
         </is>
       </c>
-      <c r="AP36" t="n">
+      <c r="BB36" t="n">
         <v>0.007679482373338938</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="BC36" t="n">
         <v>99.99744564459749</v>
       </c>
     </row>
@@ -19315,14 +20871,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19383,50 +20943,80 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>mi300::total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>mi300::total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mi300::total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mi300::total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mi300::ex_UID</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mi300::kernel_details_summary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mi300::trunc_kernel_details</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mi300::Percentage (%)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mi300::Cumulative Percentage (%)</t>
         </is>
@@ -19485,37 +21075,55 @@
         <v>4.481038411458333</v>
       </c>
       <c r="L2" t="n">
+        <v>4.481038411458333</v>
+      </c>
+      <c r="M2" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.9724400149355197</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>0.9724400149355197</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.68115234375</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
+        <v>0.68115234375</v>
+      </c>
+      <c r="S2" t="n">
         <v>5.4111328125</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
+        <v>5.4111328125</v>
+      </c>
+      <c r="U2" t="n">
         <v>107.544921875</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
+        <v>107.544921875</v>
+      </c>
+      <c r="W2" t="n">
         <v>183</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(107.545), 'mean_duration_us': np.float64(4.481041666666667), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.9520142890719772), 'min_duration_us': np.float64(0.681), 'max_duration_us': np.float64(5.411)}]</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.48)}]</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>0.3615693355478085</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>99.70364224157885</v>
       </c>
     </row>
@@ -20156,12 +21764,12 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(4015.5009999999997), 'mean_duration_us': np.float64(83.65627083333332), 'median_duration_us': np.float64(83.679), 'std_dev_duration_us': np.float64(1.1791844593401435), 'min_duration_us': np.float64(81.472), 'max_duration_us': np.float64(86.016)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 48, 'total_duration_us': np.float64(39.75), 'mean_duration_us': np.float64(0.828125), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.07937112851450877), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.057)}]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(83.66)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(83.66)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -20583,12 +22191,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(107.545), 'mean_duration_us': np.float64(4.481041666666667), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.9520142890719772), 'min_duration_us': np.float64(0.681), 'max_duration_us': np.float64(5.411)}, {'name': 'attn_fwd', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(3908.798), 'mean_duration_us': np.float64(162.86658333333332), 'median_duration_us': np.float64(164.23700000000002), 'std_dev_duration_us': np.float64(9.253315184825505), 'min_duration_us': np.float64(138.557), 'max_duration_us': np.float64(173.077)}]</t>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(3908.798), 'mean_duration_us': np.float64(162.86658333333332), 'median_duration_us': np.float64(164.23700000000002), 'std_dev_duration_us': np.float64(9.253315184825505), 'min_duration_us': np.float64(138.557), 'max_duration_us': np.float64(173.077)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(107.545), 'mean_duration_us': np.float64(4.481041666666667), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.9520142890719772), 'min_duration_us': np.float64(0.681), 'max_duration_us': np.float64(5.411)}]</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.48)}, {'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(162.87)}]</t>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(162.87)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.48)}]</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -20758,12 +22366,12 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(2266.292), 'mean_duration_us': np.float64(31.476277777777778), 'median_duration_us': np.float64(31.456), 'std_dev_duration_us': np.float64(0.31881400107892144), 'min_duration_us': np.float64(30.912), 'max_duration_us': np.float64(32.256)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 72, 'total_duration_us': np.float64(62.783), 'mean_duration_us': np.float64(0.8719861111111111), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11567921318307071), 'min_duration_us': np.float64(0.767), 'max_duration_us': np.float64(1.216)}]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.87)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.48)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.48)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.87)}]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -21605,12 +23213,12 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1814.774), 'mean_duration_us': np.float64(75.61558333333333), 'median_duration_us': np.float64(75.6315), 'std_dev_duration_us': np.float64(0.4239531142184896), 'min_duration_us': np.float64(74.752), 'max_duration_us': np.float64(76.384)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.512999999999998), 'mean_duration_us': np.float64(0.8547083333333333), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10426427926454754), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.088)}]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.85)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(75.62)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(75.62)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.85)}]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -25129,12 +26737,12 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(758.1399999999999), 'mean_duration_us': np.float64(31.58916666666666), 'median_duration_us': np.float64(31.552), 'std_dev_duration_us': np.float64(0.15096182372448408), 'min_duration_us': np.float64(31.392), 'max_duration_us': np.float64(31.936)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(20.001000000000005), 'mean_duration_us': np.float64(0.8333750000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.08185037797713582), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.056)}]</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.59)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(31.59)}, {'name': 'Memset (Device)', 'stream': 7, 'mean_duration_us': np.float64(0.83)}]</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
